--- a/questions.xlsx
+++ b/questions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://volkswagengroup-my.sharepoint.com/personal/shashanko_aditya_vwgds_in/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E4730A2-16A8-45D1-99E1-15AD17B7CF95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{8E4730A2-16A8-45D1-99E1-15AD17B7CF95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97466F19-5A76-4D8C-8F99-9889AF87D37C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BFA98757-718E-4806-A836-49C551D6B8AE}"/>
   </bookViews>
@@ -36,26 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
-  <si>
-    <t>question_id</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>question</t>
   </si>
   <si>
-    <t>option1</t>
-  </si>
-  <si>
-    <t>option2</t>
-  </si>
-  <si>
-    <t>option3</t>
-  </si>
-  <si>
-    <t>option4</t>
-  </si>
-  <si>
     <t>correct_answer</t>
   </si>
   <si>
@@ -102,6 +87,18 @@
   </si>
   <si>
     <t>ABAP</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
   </si>
 </sst>
 </file>
@@ -433,104 +430,91 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45A2639A-8327-4140-9921-4C0AE9902802}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" customWidth="1"/>
-    <col min="2" max="2" width="35.21875" customWidth="1"/>
-    <col min="3" max="7" width="18.77734375" customWidth="1"/>
+    <col min="1" max="1" width="35.21875" customWidth="1"/>
+    <col min="2" max="6" width="18.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F2" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>8</v>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
